--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0156.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0156.xlsx
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Xin chào, Rover.</t>
+          <t>Chào cậu, Rover.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Như đã hướng dẫn trước đó, ta sẽ thiết lập một bài kiểm tra cho cậu ở vùng hoang dã Kim Châu.</t>
+          <t>Như đã hướng dẫn trước đó, ta sẽ thiết lập một bài kiểm tra cho cậu ở vùng hoang dã Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Xin chào, Rover.</t>
+          <t>Chào cậu, Rover.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Như đã hướng dẫn trước đó, ta sẽ thiết lập một bài kiểm tra cho cậu ở vùng hoang dã Kim Châu.</t>
+          <t>Như đã hướng dẫn trước đó, ta sẽ thiết lập một bài kiểm tra cho cậu ở vùng hoang dã Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Xin chào, Rover.</t>
+          <t>Chào cậu, Rover.</t>
         </is>
       </c>
     </row>
